--- a/public/uploads/pusaka/presensi/sma.xlsx
+++ b/public/uploads/pusaka/presensi/sma.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="95">
   <si>
     <t>NAMA</t>
   </si>
@@ -80,220 +80,226 @@
     <t>Guru Ahli Muda</t>
   </si>
   <si>
-    <t>2026-08-01 00:00:00</t>
+    <t>2026-09-01 00:00:00</t>
+  </si>
+  <si>
+    <t>Selasa</t>
+  </si>
+  <si>
+    <t>7:30</t>
+  </si>
+  <si>
+    <t>16:0</t>
+  </si>
+  <si>
+    <t>17:35</t>
+  </si>
+  <si>
+    <t>SLTA Negeri dilingkungan Kabupaten Tanah Datar</t>
+  </si>
+  <si>
+    <t>Kantor Kementerian Agama Kabupaten Tanah Datar</t>
+  </si>
+  <si>
+    <t>PNS</t>
+  </si>
+  <si>
+    <t>2026-09-02 00:00:00</t>
+  </si>
+  <si>
+    <t>Rabu</t>
+  </si>
+  <si>
+    <t>6:30</t>
+  </si>
+  <si>
+    <t>17:39</t>
+  </si>
+  <si>
+    <t>2026-09-03 00:00:00</t>
+  </si>
+  <si>
+    <t>Kamis</t>
+  </si>
+  <si>
+    <t>7:12</t>
+  </si>
+  <si>
+    <t>2026-09-04 00:00:00</t>
+  </si>
+  <si>
+    <t>Jumat</t>
+  </si>
+  <si>
+    <t>7:9</t>
+  </si>
+  <si>
+    <t>16:30</t>
+  </si>
+  <si>
+    <t>16:53</t>
+  </si>
+  <si>
+    <t>2026-09-05 00:00:00</t>
   </si>
   <si>
     <t>Sabtu</t>
   </si>
   <si>
-    <t>SLTA Negeri dilingkungan Kabupaten Tanah Datar</t>
-  </si>
-  <si>
-    <t>Kantor Kementerian Agama Kabupaten Tanah Datar</t>
-  </si>
-  <si>
-    <t>PNS</t>
-  </si>
-  <si>
-    <t>2026-08-02 00:00:00</t>
+    <t>2026-09-06 00:00:00</t>
   </si>
   <si>
     <t>Minggu</t>
   </si>
   <si>
-    <t>2026-08-03 00:00:00</t>
+    <t>2026-09-07 00:00:00</t>
   </si>
   <si>
     <t>Senin</t>
   </si>
   <si>
-    <t>7:30</t>
-  </si>
-  <si>
-    <t>7:1</t>
-  </si>
-  <si>
-    <t>16:0</t>
-  </si>
-  <si>
-    <t>19:8</t>
-  </si>
-  <si>
-    <t>2026-08-04 00:00:00</t>
-  </si>
-  <si>
-    <t>Selasa</t>
-  </si>
-  <si>
-    <t>16:26</t>
-  </si>
-  <si>
-    <t>2026-08-05 00:00:00</t>
-  </si>
-  <si>
-    <t>Rabu</t>
-  </si>
-  <si>
-    <t>7:0</t>
-  </si>
-  <si>
-    <t>18:53</t>
-  </si>
-  <si>
-    <t>2026-08-06 00:00:00</t>
-  </si>
-  <si>
-    <t>Kamis</t>
-  </si>
-  <si>
-    <t>19:54</t>
-  </si>
-  <si>
-    <t>2026-08-07 00:00:00</t>
-  </si>
-  <si>
-    <t>Jumat</t>
+    <t>16:39</t>
+  </si>
+  <si>
+    <t>2026-09-08 00:00:00</t>
+  </si>
+  <si>
+    <t>6:59</t>
+  </si>
+  <si>
+    <t>16:43</t>
+  </si>
+  <si>
+    <t>2026-09-09 00:00:00</t>
+  </si>
+  <si>
+    <t>6:49</t>
+  </si>
+  <si>
+    <t>17:17</t>
+  </si>
+  <si>
+    <t>2026-09-10 00:00:00</t>
+  </si>
+  <si>
+    <t>17:26</t>
+  </si>
+  <si>
+    <t>2026-09-11 00:00:00</t>
+  </si>
+  <si>
+    <t>6:51</t>
+  </si>
+  <si>
+    <t>16:48</t>
+  </si>
+  <si>
+    <t>2026-09-12 00:00:00</t>
+  </si>
+  <si>
+    <t>2026-09-13 00:00:00</t>
+  </si>
+  <si>
+    <t>2026-09-14 00:00:00</t>
+  </si>
+  <si>
+    <t>6:52</t>
+  </si>
+  <si>
+    <t>17:32</t>
+  </si>
+  <si>
+    <t>2026-09-15 00:00:00</t>
+  </si>
+  <si>
+    <t>23:50</t>
+  </si>
+  <si>
+    <t>2026-09-16 00:00:00</t>
+  </si>
+  <si>
+    <t>18:16</t>
+  </si>
+  <si>
+    <t>2026-09-17 00:00:00</t>
+  </si>
+  <si>
+    <t>7:10</t>
+  </si>
+  <si>
+    <t>16:32</t>
+  </si>
+  <si>
+    <t>2026-09-18 00:00:00</t>
   </si>
   <si>
     <t>7:2</t>
   </si>
   <si>
-    <t>16:30</t>
-  </si>
-  <si>
-    <t>16:55</t>
-  </si>
-  <si>
-    <t>2026-08-08 00:00:00</t>
-  </si>
-  <si>
-    <t>2026-08-09 00:00:00</t>
-  </si>
-  <si>
-    <t>2026-08-10 00:00:00</t>
-  </si>
-  <si>
-    <t>17:29</t>
-  </si>
-  <si>
-    <t>2026-08-11 00:00:00</t>
+    <t>2026-09-19 00:00:00</t>
+  </si>
+  <si>
+    <t>2026-09-20 00:00:00</t>
+  </si>
+  <si>
+    <t>2026-09-21 00:00:00</t>
+  </si>
+  <si>
+    <t>6:48</t>
+  </si>
+  <si>
+    <t>17:40</t>
+  </si>
+  <si>
+    <t>2026-09-22 00:00:00</t>
+  </si>
+  <si>
+    <t>2026-09-23 00:00:00</t>
+  </si>
+  <si>
+    <t>6:54</t>
+  </si>
+  <si>
+    <t>16:49</t>
+  </si>
+  <si>
+    <t>2026-09-24 00:00:00</t>
+  </si>
+  <si>
+    <t>16:38</t>
+  </si>
+  <si>
+    <t>2026-09-25 00:00:00</t>
   </si>
   <si>
     <t>6:55</t>
   </si>
   <si>
-    <t>2026-08-12 00:00:00</t>
-  </si>
-  <si>
-    <t>7:7</t>
-  </si>
-  <si>
-    <t>16:25</t>
-  </si>
-  <si>
-    <t>2026-08-13 00:00:00</t>
-  </si>
-  <si>
-    <t>7:3</t>
-  </si>
-  <si>
-    <t>18:54</t>
-  </si>
-  <si>
-    <t>2026-08-14 00:00:00</t>
-  </si>
-  <si>
-    <t>18:55</t>
-  </si>
-  <si>
-    <t>2026-08-15 00:00:00</t>
-  </si>
-  <si>
-    <t>2026-08-16 00:00:00</t>
-  </si>
-  <si>
-    <t>2026-08-17 00:00:00</t>
-  </si>
-  <si>
-    <t>Proklamasi Kemerdekaan RI Ke 81</t>
-  </si>
-  <si>
-    <t>2026-08-18 00:00:00</t>
-  </si>
-  <si>
-    <t>17:0</t>
-  </si>
-  <si>
-    <t>2026-08-19 00:00:00</t>
-  </si>
-  <si>
-    <t>7:21</t>
-  </si>
-  <si>
-    <t>16:10</t>
-  </si>
-  <si>
-    <t>2026-08-20 00:00:00</t>
-  </si>
-  <si>
-    <t>7:4</t>
-  </si>
-  <si>
-    <t>16:29</t>
-  </si>
-  <si>
-    <t>2026-08-21 00:00:00</t>
-  </si>
-  <si>
-    <t>17:27</t>
-  </si>
-  <si>
-    <t>2026-08-22 00:00:00</t>
-  </si>
-  <si>
-    <t>2026-08-23 00:00:00</t>
-  </si>
-  <si>
-    <t>2026-08-24 00:00:00</t>
-  </si>
-  <si>
-    <t>2026-08-25 00:00:00</t>
-  </si>
-  <si>
-    <t>Maulid Nabi Muhammad SAW</t>
-  </si>
-  <si>
-    <t>2026-08-26 00:00:00</t>
-  </si>
-  <si>
-    <t>7:14</t>
-  </si>
-  <si>
-    <t>2026-08-27 00:00:00</t>
-  </si>
-  <si>
-    <t>7:6</t>
-  </si>
-  <si>
-    <t>16:18</t>
-  </si>
-  <si>
-    <t>2026-08-28 00:00:00</t>
-  </si>
-  <si>
-    <t>17:6</t>
-  </si>
-  <si>
-    <t>2026-08-29 00:00:00</t>
-  </si>
-  <si>
-    <t>2026-08-30 00:00:00</t>
-  </si>
-  <si>
-    <t>2026-08-31 00:00:00</t>
-  </si>
-  <si>
-    <t>17:15</t>
+    <t>2026-09-26 00:00:00</t>
+  </si>
+  <si>
+    <t>2026-09-27 00:00:00</t>
+  </si>
+  <si>
+    <t>2026-09-28 00:00:00</t>
+  </si>
+  <si>
+    <t>22:42</t>
+  </si>
+  <si>
+    <t>2026-09-29 00:00:00</t>
+  </si>
+  <si>
+    <t>6:57</t>
+  </si>
+  <si>
+    <t>17:28</t>
+  </si>
+  <si>
+    <t>2026-09-30 00:00:00</t>
+  </si>
+  <si>
+    <t>19:35</t>
   </si>
 </sst>
 </file>
@@ -633,7 +639,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:R32"/>
+  <dimension ref="A1:R31"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:18">
@@ -708,14 +714,29 @@
       <c r="E2" t="s">
         <v>22</v>
       </c>
+      <c r="F2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2">
+        <v>-225</v>
+      </c>
+      <c r="I2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2">
+        <v>95</v>
+      </c>
       <c r="P2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Q2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="R2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -729,19 +750,37 @@
         <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E3" t="s">
-        <v>27</v>
+        <v>30</v>
+      </c>
+      <c r="F3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3">
+        <v>60</v>
+      </c>
+      <c r="I3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K3">
+        <v>99</v>
       </c>
       <c r="P3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Q3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="R3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -755,37 +794,34 @@
         <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E4" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F4" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H4">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I4" t="s">
-        <v>32</v>
-      </c>
-      <c r="J4" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="K4">
-        <v>188</v>
+        <v>-255</v>
       </c>
       <c r="P4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Q4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="R4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -799,37 +835,37 @@
         <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F5" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G5" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="H5">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I5" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="J5" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="K5">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="P5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Q5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="R5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -843,37 +879,19 @@
         <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E6" t="s">
-        <v>38</v>
-      </c>
-      <c r="F6" t="s">
-        <v>30</v>
-      </c>
-      <c r="G6" t="s">
-        <v>39</v>
-      </c>
-      <c r="H6">
-        <v>30</v>
-      </c>
-      <c r="I6" t="s">
-        <v>32</v>
-      </c>
-      <c r="J6" t="s">
-        <v>40</v>
-      </c>
-      <c r="K6">
-        <v>173</v>
+        <v>42</v>
       </c>
       <c r="P6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Q6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="R6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -887,37 +905,19 @@
         <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E7" t="s">
-        <v>42</v>
-      </c>
-      <c r="F7" t="s">
-        <v>30</v>
-      </c>
-      <c r="G7" t="s">
-        <v>31</v>
-      </c>
-      <c r="H7">
-        <v>29</v>
-      </c>
-      <c r="I7" t="s">
-        <v>32</v>
-      </c>
-      <c r="J7" t="s">
-        <v>43</v>
-      </c>
-      <c r="K7">
-        <v>234</v>
+        <v>44</v>
       </c>
       <c r="P7" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Q7" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="R7" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -931,37 +931,34 @@
         <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F8" t="s">
-        <v>30</v>
-      </c>
-      <c r="G8" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H8">
-        <v>28</v>
+        <v>-225</v>
       </c>
       <c r="I8" t="s">
+        <v>24</v>
+      </c>
+      <c r="J8" t="s">
         <v>47</v>
       </c>
-      <c r="J8" t="s">
-        <v>48</v>
-      </c>
       <c r="K8">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="P8" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Q8" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="R8" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -975,19 +972,37 @@
         <v>20</v>
       </c>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E9" t="s">
         <v>22</v>
       </c>
+      <c r="F9" t="s">
+        <v>23</v>
+      </c>
+      <c r="G9" t="s">
+        <v>49</v>
+      </c>
+      <c r="H9">
+        <v>31</v>
+      </c>
+      <c r="I9" t="s">
+        <v>24</v>
+      </c>
+      <c r="J9" t="s">
+        <v>50</v>
+      </c>
+      <c r="K9">
+        <v>43</v>
+      </c>
       <c r="P9" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Q9" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="R9" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1001,19 +1016,37 @@
         <v>20</v>
       </c>
       <c r="D10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E10" t="s">
-        <v>27</v>
+        <v>30</v>
+      </c>
+      <c r="F10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" t="s">
+        <v>52</v>
+      </c>
+      <c r="H10">
+        <v>41</v>
+      </c>
+      <c r="I10" t="s">
+        <v>24</v>
+      </c>
+      <c r="J10" t="s">
+        <v>53</v>
+      </c>
+      <c r="K10">
+        <v>77</v>
       </c>
       <c r="P10" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Q10" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="R10" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1027,37 +1060,34 @@
         <v>20</v>
       </c>
       <c r="D11" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E11" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F11" t="s">
-        <v>30</v>
-      </c>
-      <c r="G11" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="H11">
-        <v>29</v>
+        <v>-225</v>
       </c>
       <c r="I11" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J11" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K11">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="P11" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Q11" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="R11" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1071,37 +1101,37 @@
         <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E12" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F12" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G12" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="H12">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I12" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="J12" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="K12">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="P12" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Q12" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="R12" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1115,37 +1145,19 @@
         <v>20</v>
       </c>
       <c r="D13" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E13" t="s">
-        <v>38</v>
-      </c>
-      <c r="F13" t="s">
-        <v>30</v>
-      </c>
-      <c r="G13" t="s">
-        <v>56</v>
-      </c>
-      <c r="H13">
-        <v>23</v>
-      </c>
-      <c r="I13" t="s">
-        <v>32</v>
-      </c>
-      <c r="J13" t="s">
-        <v>57</v>
-      </c>
-      <c r="K13">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="P13" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Q13" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="R13" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -1159,37 +1171,19 @@
         <v>20</v>
       </c>
       <c r="D14" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E14" t="s">
-        <v>42</v>
-      </c>
-      <c r="F14" t="s">
-        <v>30</v>
-      </c>
-      <c r="G14" t="s">
-        <v>59</v>
-      </c>
-      <c r="H14">
-        <v>27</v>
-      </c>
-      <c r="I14" t="s">
-        <v>32</v>
-      </c>
-      <c r="J14" t="s">
-        <v>60</v>
-      </c>
-      <c r="K14">
-        <v>174</v>
+        <v>44</v>
       </c>
       <c r="P14" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Q14" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="R14" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -1206,34 +1200,34 @@
         <v>61</v>
       </c>
       <c r="E15" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F15" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G15" t="s">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="H15">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="I15" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="J15" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K15">
-        <v>145</v>
+        <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Q15" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="R15" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -1247,19 +1241,34 @@
         <v>20</v>
       </c>
       <c r="D16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E16" t="s">
         <v>22</v>
       </c>
+      <c r="F16" t="s">
+        <v>23</v>
+      </c>
+      <c r="H16">
+        <v>-225</v>
+      </c>
+      <c r="I16" t="s">
+        <v>24</v>
+      </c>
+      <c r="J16" t="s">
+        <v>65</v>
+      </c>
+      <c r="K16">
+        <v>470</v>
+      </c>
       <c r="P16" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Q16" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="R16" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -1273,19 +1282,34 @@
         <v>20</v>
       </c>
       <c r="D17" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E17" t="s">
-        <v>27</v>
+        <v>30</v>
+      </c>
+      <c r="F17" t="s">
+        <v>23</v>
+      </c>
+      <c r="H17">
+        <v>-225</v>
+      </c>
+      <c r="I17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J17" t="s">
+        <v>67</v>
+      </c>
+      <c r="K17">
+        <v>136</v>
       </c>
       <c r="P17" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Q17" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="R17" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -1299,28 +1323,37 @@
         <v>20</v>
       </c>
       <c r="D18" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E18" t="s">
-        <v>29</v>
+        <v>34</v>
+      </c>
+      <c r="F18" t="s">
+        <v>23</v>
+      </c>
+      <c r="G18" t="s">
+        <v>69</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>20</v>
+      </c>
+      <c r="I18" t="s">
+        <v>24</v>
+      </c>
+      <c r="J18" t="s">
+        <v>70</v>
       </c>
       <c r="K18">
-        <v>0</v>
-      </c>
-      <c r="L18" t="s">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="P18" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Q18" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="R18" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -1334,37 +1367,34 @@
         <v>20</v>
       </c>
       <c r="D19" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E19" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F19" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G19" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="H19">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I19" t="s">
-        <v>32</v>
-      </c>
-      <c r="J19" t="s">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="K19">
-        <v>60</v>
+        <v>-255</v>
       </c>
       <c r="P19" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Q19" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="R19" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -1378,37 +1408,19 @@
         <v>20</v>
       </c>
       <c r="D20" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E20" t="s">
-        <v>38</v>
-      </c>
-      <c r="F20" t="s">
-        <v>30</v>
-      </c>
-      <c r="G20" t="s">
-        <v>70</v>
-      </c>
-      <c r="H20">
-        <v>9</v>
-      </c>
-      <c r="I20" t="s">
-        <v>32</v>
-      </c>
-      <c r="J20" t="s">
-        <v>71</v>
-      </c>
-      <c r="K20">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="P20" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Q20" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="R20" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -1422,37 +1434,19 @@
         <v>20</v>
       </c>
       <c r="D21" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E21" t="s">
-        <v>42</v>
-      </c>
-      <c r="F21" t="s">
-        <v>30</v>
-      </c>
-      <c r="G21" t="s">
-        <v>73</v>
-      </c>
-      <c r="H21">
-        <v>26</v>
-      </c>
-      <c r="I21" t="s">
-        <v>32</v>
-      </c>
-      <c r="J21" t="s">
-        <v>74</v>
-      </c>
-      <c r="K21">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="P21" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Q21" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="R21" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -1469,34 +1463,34 @@
         <v>75</v>
       </c>
       <c r="E22" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F22" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G22" t="s">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="H22">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="I22" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="J22" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K22">
-        <v>57</v>
+        <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Q22" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="R22" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -1510,19 +1504,37 @@
         <v>20</v>
       </c>
       <c r="D23" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E23" t="s">
         <v>22</v>
       </c>
+      <c r="F23" t="s">
+        <v>23</v>
+      </c>
+      <c r="G23" t="s">
+        <v>72</v>
+      </c>
+      <c r="H23">
+        <v>28</v>
+      </c>
+      <c r="I23" t="s">
+        <v>24</v>
+      </c>
+      <c r="J23" t="s">
+        <v>50</v>
+      </c>
+      <c r="K23">
+        <v>43</v>
+      </c>
       <c r="P23" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Q23" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="R23" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -1536,19 +1548,37 @@
         <v>20</v>
       </c>
       <c r="D24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E24" t="s">
-        <v>27</v>
+        <v>30</v>
+      </c>
+      <c r="F24" t="s">
+        <v>23</v>
+      </c>
+      <c r="G24" t="s">
+        <v>80</v>
+      </c>
+      <c r="H24">
+        <v>36</v>
+      </c>
+      <c r="I24" t="s">
+        <v>24</v>
+      </c>
+      <c r="J24" t="s">
+        <v>81</v>
+      </c>
+      <c r="K24">
+        <v>49</v>
       </c>
       <c r="P24" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Q24" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="R24" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:18">
@@ -1562,37 +1592,37 @@
         <v>20</v>
       </c>
       <c r="D25" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E25" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F25" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G25" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="H25">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="I25" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J25" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="K25">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="P25" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Q25" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="R25" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:18">
@@ -1606,28 +1636,37 @@
         <v>20</v>
       </c>
       <c r="D26" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E26" t="s">
+        <v>37</v>
+      </c>
+      <c r="F26" t="s">
+        <v>23</v>
+      </c>
+      <c r="G26" t="s">
+        <v>85</v>
+      </c>
+      <c r="H26">
         <v>35</v>
       </c>
-      <c r="H26">
-        <v>0</v>
+      <c r="I26" t="s">
+        <v>39</v>
+      </c>
+      <c r="J26" t="s">
+        <v>58</v>
       </c>
       <c r="K26">
-        <v>0</v>
-      </c>
-      <c r="L26" t="s">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="P26" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Q26" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="R26" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" spans="1:18">
@@ -1641,37 +1680,19 @@
         <v>20</v>
       </c>
       <c r="D27" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E27" t="s">
-        <v>38</v>
-      </c>
-      <c r="F27" t="s">
-        <v>30</v>
-      </c>
-      <c r="G27" t="s">
-        <v>83</v>
-      </c>
-      <c r="H27">
-        <v>16</v>
-      </c>
-      <c r="I27" t="s">
-        <v>32</v>
-      </c>
-      <c r="J27" t="s">
-        <v>32</v>
-      </c>
-      <c r="K27">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="P27" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Q27" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="R27" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" spans="1:18">
@@ -1685,37 +1706,19 @@
         <v>20</v>
       </c>
       <c r="D28" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E28" t="s">
-        <v>42</v>
-      </c>
-      <c r="F28" t="s">
-        <v>30</v>
-      </c>
-      <c r="G28" t="s">
-        <v>85</v>
-      </c>
-      <c r="H28">
-        <v>24</v>
-      </c>
-      <c r="I28" t="s">
-        <v>32</v>
-      </c>
-      <c r="J28" t="s">
-        <v>86</v>
-      </c>
-      <c r="K28">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="P28" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Q28" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="R28" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:18">
@@ -1729,34 +1732,37 @@
         <v>20</v>
       </c>
       <c r="D29" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E29" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F29" t="s">
-        <v>30</v>
+        <v>23</v>
+      </c>
+      <c r="G29" t="s">
+        <v>57</v>
       </c>
       <c r="H29">
-        <v>-225</v>
+        <v>39</v>
       </c>
       <c r="I29" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="J29" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K29">
-        <v>36</v>
+        <v>402</v>
       </c>
       <c r="P29" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Q29" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="R29" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30" spans="1:18">
@@ -1770,19 +1776,37 @@
         <v>20</v>
       </c>
       <c r="D30" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E30" t="s">
         <v>22</v>
       </c>
+      <c r="F30" t="s">
+        <v>23</v>
+      </c>
+      <c r="G30" t="s">
+        <v>91</v>
+      </c>
+      <c r="H30">
+        <v>33</v>
+      </c>
+      <c r="I30" t="s">
+        <v>24</v>
+      </c>
+      <c r="J30" t="s">
+        <v>92</v>
+      </c>
+      <c r="K30">
+        <v>88</v>
+      </c>
       <c r="P30" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Q30" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="R30" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31" spans="1:18">
@@ -1796,63 +1820,37 @@
         <v>20</v>
       </c>
       <c r="D31" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E31" t="s">
-        <v>27</v>
+        <v>30</v>
+      </c>
+      <c r="F31" t="s">
+        <v>23</v>
+      </c>
+      <c r="G31" t="s">
+        <v>62</v>
+      </c>
+      <c r="H31">
+        <v>38</v>
+      </c>
+      <c r="I31" t="s">
+        <v>24</v>
+      </c>
+      <c r="J31" t="s">
+        <v>94</v>
+      </c>
+      <c r="K31">
+        <v>215</v>
       </c>
       <c r="P31" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Q31" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="R31" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18">
-      <c r="A32" t="s">
-        <v>18</v>
-      </c>
-      <c r="B32" t="s">
-        <v>19</v>
-      </c>
-      <c r="C32" t="s">
-        <v>20</v>
-      </c>
-      <c r="D32" t="s">
-        <v>91</v>
-      </c>
-      <c r="E32" t="s">
-        <v>29</v>
-      </c>
-      <c r="F32" t="s">
-        <v>30</v>
-      </c>
-      <c r="G32" t="s">
-        <v>46</v>
-      </c>
-      <c r="H32">
-        <v>28</v>
-      </c>
-      <c r="I32" t="s">
-        <v>32</v>
-      </c>
-      <c r="J32" t="s">
-        <v>92</v>
-      </c>
-      <c r="K32">
-        <v>75</v>
-      </c>
-      <c r="P32" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q32" t="s">
-        <v>24</v>
-      </c>
-      <c r="R32" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
